--- a/REMOTO/Accesos RDP 1.xlsx
+++ b/REMOTO/Accesos RDP 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://castraining365-my.sharepoint.com/personal/luis_gonzalez_cas-training_com/Documents/Archivos de chat de Microsoft Teams/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\antonio2\TRABAJO\CURSOS\C++ Microservicios\repositorio\REMOTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{92037095-9B20-434E-9FF9-B2E7FBF951BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0474D33-844F-492A-B647-74D1BF4C9166}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C8AFC6-CE25-420E-8032-46E8F5BCB735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4575" yWindow="1770" windowWidth="21600" windowHeight="11295" xr2:uid="{867DC5EE-8D59-45E8-84B9-31D2579529E7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{867DC5EE-8D59-45E8-84B9-31D2579529E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="75">
   <si>
     <t>APELLIDOS</t>
   </si>
@@ -204,13 +204,70 @@
   </si>
   <si>
     <t>Pa55w.rd</t>
+  </si>
+  <si>
+    <t>Aitor</t>
+  </si>
+  <si>
+    <t>Jose Berriales</t>
+  </si>
+  <si>
+    <t>Carlos Espinoza</t>
+  </si>
+  <si>
+    <t>Javier Comas</t>
+  </si>
+  <si>
+    <t>Daniel Martinez</t>
+  </si>
+  <si>
+    <t>Aida</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>Jaime</t>
+  </si>
+  <si>
+    <t>Jose A.</t>
+  </si>
+  <si>
+    <t>Jose Antonio Maheso</t>
+  </si>
+  <si>
+    <t>Jose Maria Arias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Manuel </t>
+  </si>
+  <si>
+    <t>Luis Fernando</t>
+  </si>
+  <si>
+    <t>Javier Martinez</t>
+  </si>
+  <si>
+    <t>Miguel Hernandez</t>
+  </si>
+  <si>
+    <t>Ruben Ruiz</t>
+  </si>
+  <si>
+    <t>Mario Zarzulo</t>
+  </si>
+  <si>
+    <t>sin VPN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,6 +293,54 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,7 +391,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -297,9 +402,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -653,10 +773,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -681,56 +801,65 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="C2" t="s">
+    <row r="2" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="C3" t="s">
+      <c r="F2" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13"/>
+      <c r="B3" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="F3" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="15" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
@@ -749,12 +878,15 @@
       <c r="H4" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
+      <c r="B5" s="9" t="s">
+        <v>59</v>
+      </c>
       <c r="C5" t="s">
         <v>15</v>
       </c>
@@ -773,84 +905,96 @@
       <c r="H5" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="C6" t="s">
+      <c r="I5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="C7" t="s">
+      <c r="F6" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="C8" t="s">
+      <c r="F7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="5" t="s">
+      <c r="F8" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
+      <c r="B9" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="C9" t="s">
         <v>19</v>
       </c>
@@ -869,247 +1013,279 @@
       <c r="H9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="C10" t="s">
+      <c r="I9" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6"/>
+      <c r="B10" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="C11" t="s">
+      <c r="F10" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="C12" t="s">
+      <c r="F11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="D12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="C13" t="s">
+      <c r="F12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+      <c r="B13" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" t="s">
-        <v>55</v>
-      </c>
-      <c r="H13" t="s">
-        <v>11</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="C14" t="s">
+      <c r="F13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="D14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H14" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="C15" t="s">
+      <c r="F14" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13"/>
+      <c r="B15" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="D15" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" t="s">
-        <v>11</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="C16" t="s">
+      <c r="F15" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="D16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" t="s">
-        <v>55</v>
-      </c>
-      <c r="H16" t="s">
-        <v>11</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="C17" t="s">
+      <c r="F16" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
+      <c r="B17" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="D17" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" t="s">
-        <v>55</v>
-      </c>
-      <c r="H17" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="C18" t="s">
+      <c r="F17" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10"/>
+      <c r="B18" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="D18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18" t="s">
-        <v>55</v>
-      </c>
-      <c r="H18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="C19" t="s">
+      <c r="F18" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="D19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H19" t="s">
-        <v>11</v>
-      </c>
-      <c r="I19" s="5" t="s">
+      <c r="F19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1133,7 +1309,7 @@
       <c r="H20" t="s">
         <v>11</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1157,7 +1333,7 @@
       <c r="H21" t="s">
         <v>11</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1181,7 +1357,7 @@
       <c r="H22" t="s">
         <v>11</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="4" t="s">
         <v>12</v>
       </c>
     </row>

--- a/REMOTO/Accesos RDP 1.xlsx
+++ b/REMOTO/Accesos RDP 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\antonio2\TRABAJO\CURSOS\C++ Microservicios\repositorio\REMOTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C8AFC6-CE25-420E-8032-46E8F5BCB735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DD2DD6D-24F9-4860-8717-59A8DB9D7615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{867DC5EE-8D59-45E8-84B9-31D2579529E7}"/>
   </bookViews>

--- a/REMOTO/Accesos RDP 1.xlsx
+++ b/REMOTO/Accesos RDP 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\antonio2\TRABAJO\CURSOS\C++ Microservicios\repositorio\REMOTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DD2DD6D-24F9-4860-8717-59A8DB9D7615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843D7710-44A3-4CA5-9653-7262BDFB991B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{867DC5EE-8D59-45E8-84B9-31D2579529E7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="76">
   <si>
     <t>APELLIDOS</t>
   </si>
@@ -260,14 +260,17 @@
     <t>Mario Zarzulo</t>
   </si>
   <si>
-    <t>sin VPN</t>
+    <t>no funciona</t>
+  </si>
+  <si>
+    <t>Alfredo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -345,13 +348,43 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -391,7 +424,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -420,6 +453,13 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -990,30 +1030,32 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="9" t="s">
+    <row r="9" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D9" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="4" t="s">
+      <c r="F9" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="20" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1045,9 +1087,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>74</v>
-      </c>
+      <c r="A11" s="6"/>
       <c r="B11" s="5" t="s">
         <v>65</v>
       </c>
@@ -1315,6 +1355,9 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
       <c r="C21" t="s">
         <v>31</v>
       </c>
@@ -1339,6 +1382,9 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
       <c r="C22" t="s">
         <v>32</v>
       </c>

--- a/REMOTO/Accesos RDP 1.xlsx
+++ b/REMOTO/Accesos RDP 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\antonio2\TRABAJO\CURSOS\C++ Microservicios\repositorio\REMOTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843D7710-44A3-4CA5-9653-7262BDFB991B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9839574-5306-4775-AEF7-034FDD845A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{867DC5EE-8D59-45E8-84B9-31D2579529E7}"/>
   </bookViews>
@@ -373,7 +373,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -383,6 +383,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,7 +430,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -460,6 +466,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -900,10 +907,10 @@
       <c r="B4" t="s">
         <v>58</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="21" t="s">
         <v>10</v>
       </c>
       <c r="E4" t="s">

--- a/REMOTO/Accesos RDP 1.xlsx
+++ b/REMOTO/Accesos RDP 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\antonio2\TRABAJO\CURSOS\C++ Microservicios\repositorio\REMOTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9839574-5306-4775-AEF7-034FDD845A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82D4A00-9F1A-4247-9DED-776C5776B612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{867DC5EE-8D59-45E8-84B9-31D2579529E7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="68">
   <si>
     <t>APELLIDOS</t>
   </si>
@@ -206,71 +206,47 @@
     <t>Pa55w.rd</t>
   </si>
   <si>
-    <t>Aitor</t>
-  </si>
-  <si>
-    <t>Jose Berriales</t>
-  </si>
-  <si>
-    <t>Carlos Espinoza</t>
-  </si>
-  <si>
-    <t>Javier Comas</t>
-  </si>
-  <si>
-    <t>Daniel Martinez</t>
-  </si>
-  <si>
-    <t>Aida</t>
-  </si>
-  <si>
-    <t>Francisco</t>
-  </si>
-  <si>
-    <t>Gonzalo</t>
-  </si>
-  <si>
-    <t>Jaime</t>
-  </si>
-  <si>
-    <t>Jose A.</t>
-  </si>
-  <si>
-    <t>Jose Antonio Maheso</t>
-  </si>
-  <si>
-    <t>Jose Maria Arias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Manuel </t>
-  </si>
-  <si>
-    <t>Luis Fernando</t>
-  </si>
-  <si>
-    <t>Javier Martinez</t>
-  </si>
-  <si>
-    <t>Miguel Hernandez</t>
-  </si>
-  <si>
-    <t>Ruben Ruiz</t>
-  </si>
-  <si>
-    <t>Mario Zarzulo</t>
-  </si>
-  <si>
-    <t>no funciona</t>
-  </si>
-  <si>
-    <t>Alfredo</t>
+    <t>Zuñiga Gonzalez</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>Garcia Garcia</t>
+  </si>
+  <si>
+    <t>Juan Pedro</t>
+  </si>
+  <si>
+    <t>Belzunegui Gabilondo</t>
+  </si>
+  <si>
+    <t>Ignacio</t>
+  </si>
+  <si>
+    <t>Lucas Hernandez</t>
+  </si>
+  <si>
+    <t>Sergio</t>
+  </si>
+  <si>
+    <t>Hontanaya Martinez</t>
+  </si>
+  <si>
+    <t>Juan Andres</t>
+  </si>
+  <si>
+    <t>Gonzalez Perea</t>
+  </si>
+  <si>
+    <t>Lucia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,97 +276,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -430,7 +322,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -441,32 +333,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -809,7 +678,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.42578125" bestFit="1" customWidth="1"/>
@@ -820,10 +689,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -848,69 +717,75 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="5" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="14" t="s">
+      <c r="F2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="14" t="s">
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="15" t="s">
+      <c r="F3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
+      <c r="A4" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="B4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="E4" t="s">
@@ -925,14 +800,16 @@
       <c r="H4" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="9" t="s">
-        <v>59</v>
+      <c r="A5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
@@ -952,387 +829,353 @@
       <c r="H5" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="14" t="s">
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="C8" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="14" t="s">
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="19" t="s">
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="19" t="s">
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="C11" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="C12" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="9" t="s">
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
-      <c r="B13" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="C13" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="9" t="s">
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="C14" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="14" t="s">
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="C15" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="14" t="s">
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="C16" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="9" t="s">
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="14" t="s">
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="C17" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="14" t="s">
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" t="s">
+        <v>55</v>
+      </c>
+      <c r="H17" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="C18" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="9" t="s">
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-      <c r="B19" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="C19" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
         <v>50</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I19" s="7" t="s">
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1356,15 +1199,12 @@
       <c r="H20" t="s">
         <v>11</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
       <c r="C21" t="s">
         <v>31</v>
       </c>
@@ -1383,15 +1223,12 @@
       <c r="H21" t="s">
         <v>11</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
       <c r="C22" t="s">
         <v>32</v>
       </c>
@@ -1410,7 +1247,7 @@
       <c r="H22" t="s">
         <v>11</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="5" t="s">
         <v>12</v>
       </c>
     </row>

--- a/REMOTO/Accesos RDP 1.xlsx
+++ b/REMOTO/Accesos RDP 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\antonio2\TRABAJO\CURSOS\C++ Microservicios\repositorio\REMOTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82D4A00-9F1A-4247-9DED-776C5776B612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7952CEEC-387B-49F5-9A3A-2A3A21E98211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{867DC5EE-8D59-45E8-84B9-31D2579529E7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{867DC5EE-8D59-45E8-84B9-31D2579529E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="70">
   <si>
     <t>APELLIDOS</t>
   </si>
@@ -240,13 +240,19 @@
   </si>
   <si>
     <t>Lucia</t>
+  </si>
+  <si>
+    <t>Fernandez Ruis</t>
+  </si>
+  <si>
+    <t>Mario</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,6 +278,21 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,7 +343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -333,9 +354,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -679,7 +705,7 @@
   <cols>
     <col min="1" max="1" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
@@ -689,10 +715,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -717,148 +743,148 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="F2" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="F3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="F4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="F5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="5" t="s">
+      <c r="F6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -887,36 +913,40 @@
       <c r="H7" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="C8" t="s">
+      <c r="I7" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="5" t="s">
+      <c r="F8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
       <c r="C9" t="s">
         <v>19</v>
       </c>
@@ -935,7 +965,7 @@
       <c r="H9" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -959,7 +989,7 @@
       <c r="H10" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -983,7 +1013,7 @@
       <c r="H11" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1007,7 +1037,7 @@
       <c r="H12" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1031,7 +1061,7 @@
       <c r="H13" t="s">
         <v>11</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1055,7 +1085,7 @@
       <c r="H14" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1079,7 +1109,7 @@
       <c r="H15" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1103,7 +1133,7 @@
       <c r="H16" t="s">
         <v>11</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1127,7 +1157,7 @@
       <c r="H17" t="s">
         <v>11</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1151,7 +1181,7 @@
       <c r="H18" t="s">
         <v>11</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1175,7 +1205,7 @@
       <c r="H19" t="s">
         <v>11</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1199,7 +1229,7 @@
       <c r="H20" t="s">
         <v>11</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1223,7 +1253,7 @@
       <c r="H21" t="s">
         <v>11</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1247,7 +1277,7 @@
       <c r="H22" t="s">
         <v>11</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="4" t="s">
         <v>12</v>
       </c>
     </row>
